--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4051</v>
+        <v>3.4409</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9662</v>
+        <v>4.0301</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2727</v>
+        <v>1.3255</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1371</v>
+        <v>1.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8013</v>
+        <v>1.8808</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8013</v>
+        <v>1.8808</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6726</v>
+        <v>1.6411</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9051</v>
+        <v>1.8698</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2325</v>
+        <v>-0.2287</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3836</v>
+        <v>1.4571</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4473</v>
+        <v>1.5926</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9104</v>
+        <v>0.9644</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.983</v>
+        <v>-0.9272</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8934</v>
+        <v>1.8916</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4253</v>
+        <v>1.5328</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4544</v>
+        <v>-0.3719</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8797</v>
+        <v>1.9047</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5149</v>
+        <v>-0.5684</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0134</v>
+        <v>0.0185</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2378</v>
+        <v>-0.2196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2511</v>
+        <v>0.2381</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3775</v>
+        <v>1.3706</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.299</v>
+        <v>-0.1903</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6765</v>
+        <v>1.5609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6373</v>
+        <v>0.6795</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1763</v>
+        <v>-0.118</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8136</v>
+        <v>0.7974</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0546</v>
+        <v>0.0386</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0546</v>
+        <v>0.0386</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6918</v>
+        <v>0.6409</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8136</v>
+        <v>0.7974</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2445</v>
+        <v>-0.2289</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2442</v>
+        <v>0.2258</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2138</v>
+        <v>0.1517</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3121</v>
+        <v>0.4763</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0983</v>
+        <v>-0.3246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3005</v>
+        <v>0.2677</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3232</v>
+        <v>1.4215</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3232</v>
+        <v>1.4215</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0227</v>
+        <v>-1.1538</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6733</v>
+        <v>1.6503</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0297</v>
+        <v>2.0148</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3564</v>
+        <v>-0.3645</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5602</v>
+        <v>-2.5453</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.0406</v>
+        <v>-1.9863</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6794</v>
+        <v>-0.6444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2084</v>
+        <v>0.4632</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8879</v>
+        <v>-1.1076</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2692</v>
+        <v>-2.2545</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.5685</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6417</v>
+        <v>-1.686</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1891</v>
+        <v>-0.006</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0869</v>
+        <v>1.242</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.276</v>
+        <v>-1.248</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0801</v>
+        <v>-2.2485</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7144</v>
+        <v>-1.8105</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3657</v>
+        <v>-0.4381</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8704</v>
+        <v>-0.8378</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4622</v>
+        <v>-0.4208</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4082</v>
+        <v>-0.417</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3254</v>
+        <v>-1.3626</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0878</v>
+        <v>-0.9721</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2376</v>
+        <v>-0.3906</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6352</v>
+        <v>-1.6655</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3357</v>
+        <v>-2.3348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7005</v>
+        <v>0.6693</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3344</v>
+        <v>-0.2577</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0143</v>
+        <v>-0.9467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3009</v>
+        <v>-1.4078</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3214</v>
+        <v>-1.3881</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3099</v>
+        <v>0.3029</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2469</v>
+        <v>0.2594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.063</v>
+        <v>0.0435</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7974</v>
+        <v>-1.7731</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1849</v>
+        <v>-1.9368</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3875</v>
+        <v>0.1638</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8537</v>
+        <v>-0.829</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5442</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3979</v>
+        <v>-1.394</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1089</v>
+        <v>0.0603</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3232</v>
+        <v>1.4215</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4322</v>
+        <v>-1.3612</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7447</v>
+        <v>-0.8893</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.779</v>
+        <v>-0.8565</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2841</v>
+        <v>-1.2488</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0757</v>
+        <v>-1.0235</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2084</v>
+        <v>-0.2253</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8186</v>
+        <v>-1.8147</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8591</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9594</v>
+        <v>-1.0884</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.349</v>
+        <v>-2.3461</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1561</v>
+        <v>-1.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.193</v>
+        <v>-1.2224</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7126</v>
+        <v>-0.6054</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0346</v>
+        <v>0.0591</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6365</v>
+        <v>-1.7407</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.637</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1466</v>
+        <v>-0.1209</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5233</v>
+        <v>-0.5161</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1909</v>
+        <v>-2.2755</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.4857</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.637</v>
+        <v>-1.7898</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5152</v>
+        <v>-2.5503</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8159</v>
+        <v>-1.8011</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6993</v>
+        <v>-0.7492</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2142</v>
+        <v>-1.153</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2942</v>
+        <v>-1.234</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.301</v>
+        <v>-1.3973</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5671</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9117</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6603</v>
+        <v>0.6673</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2636</v>
+        <v>0.2444</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5001</v>
+        <v>-2.4804</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3652</v>
+        <v>-2.3032</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1348</v>
+        <v>-0.1772</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.507</v>
+        <v>-2.4927</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7003</v>
+        <v>-1.6887</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8067</v>
+        <v>-0.804</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.914</v>
+        <v>-1.8704</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.236</v>
+        <v>-1.2059</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.593</v>
+        <v>-0.6224</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3932</v>
+        <v>-0.3772</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U11" t="n">
-        <v>0.058</v>
+        <v>0.0557</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4203</v>
+        <v>-5.3309</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0022</v>
+        <v>-4.6095</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4181</v>
+        <v>-0.7214</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.1847</v>
+        <v>-5.1835</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2427</v>
+        <v>-2.2203</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9421</v>
+        <v>-2.9632</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9829</v>
+        <v>-2.7784</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2709</v>
+        <v>-0.1204</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2018</v>
+        <v>-2.4051</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2301</v>
+        <v>-0.3052</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9552</v>
+        <v>-1.901</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.398</v>
+        <v>-1.3327</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5572</v>
+        <v>-0.5684</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2398</v>
+        <v>-6.2388</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8163</v>
+        <v>-4.5447</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4234</v>
+        <v>-1.694</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.01</v>
+        <v>-6.9555</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2135</v>
+        <v>-1.2079</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.7965</v>
+        <v>-5.7476</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.6588</v>
+        <v>-4.4359</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7652</v>
+        <v>0.8802</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.424</v>
+        <v>-5.316</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3512</v>
+        <v>-2.5196</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9787</v>
+        <v>-2.0881</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1701</v>
+        <v>2.1325</v>
       </c>
       <c r="T13" t="n">
-        <v>1.843</v>
+        <v>1.8385</v>
       </c>
       <c r="U13" t="n">
-        <v>0.327</v>
+        <v>0.294</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.5919</v>
+        <v>-15.5001</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.2344</v>
+        <v>-9.206399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.3572</v>
+        <v>-6.293600000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.2031</v>
+        <v>-21.04</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.561</v>
+        <v>-10.211</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.6423</v>
+        <v>-10.8291</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.6197</v>
+        <v>-6.172800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9408</v>
+        <v>3.0648</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.560600000000001</v>
+        <v>-9.237500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.5836</v>
+        <v>-14.8673</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.5018</v>
+        <v>-13.276</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0817</v>
+        <v>-1.5915</v>
       </c>
       <c r="P14" t="n">
-        <v>7.0021</v>
+        <v>6.815700000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.0021</v>
+        <v>-6.8159</v>
       </c>
       <c r="R14" t="n">
-        <v>14.0041</v>
+        <v>13.6315</v>
       </c>
       <c r="S14" t="n">
-        <v>1.590200000000001</v>
+        <v>1.6522</v>
       </c>
       <c r="T14" t="n">
-        <v>2.669</v>
+        <v>2.8706</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0791</v>
+        <v>-1.2185</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.9806</v>
+        <v>-2.928</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7180000000000001</v>
+        <v>0.9117000000000003</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.6986</v>
+        <v>-3.839700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4409</v>
+        <v>2.4998</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0301</v>
+        <v>3.0333</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5336</v>
       </c>
       <c r="G2" t="n">
         <v>1.3255</v>
@@ -610,13 +610,13 @@
         <v>0.1947</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6411</v>
+        <v>0.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8698</v>
+        <v>0.8731</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2287</v>
+        <v>-0.1731</v>
       </c>
       <c r="V2" t="n">
         <v>0.2795</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>S. LAPUSTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4571</v>
+        <v>2.1178</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5926</v>
+        <v>0.5074</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1355</v>
+        <v>1.6103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9644</v>
+        <v>0.6795</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9272</v>
+        <v>-0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8916</v>
+        <v>0.7974</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5328</v>
+        <v>0.0386</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3719</v>
+        <v>0.0386</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9047</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5684</v>
+        <v>0.6409</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5553</v>
+        <v>-0.1565</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0131</v>
+        <v>0.7974</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0185</v>
+        <v>0.7441</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2196</v>
+        <v>0.4689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2381</v>
+        <v>0.2753</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2795</v>
+        <v>-0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LAPUSTE</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3706</v>
+        <v>1.7561</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1903</v>
+        <v>1.8917</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5609</v>
+        <v>-0.1355</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6795</v>
+        <v>0.9644</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.118</v>
+        <v>-0.9272</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7974</v>
+        <v>1.8916</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0386</v>
+        <v>1.5328</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0386</v>
+        <v>-0.3719</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.9047</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6409</v>
+        <v>-0.5684</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1565</v>
+        <v>-0.5553</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7974</v>
+        <v>-0.0131</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9737</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9737</v>
+        <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.003</v>
+        <v>0.3175</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2289</v>
+        <v>0.0794</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2258</v>
+        <v>0.2381</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2795</v>
+        <v>0.2795</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1517</v>
+        <v>-0.1569</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4763</v>
+        <v>0.7622</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3246</v>
+        <v>-0.9191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2677</v>
+        <v>-2.2545</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0216</v>
+        <v>-0.5685</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2461</v>
+        <v>-1.686</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4215</v>
+        <v>-0.006</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4215</v>
+        <v>1.242</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.248</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1538</v>
+        <v>-2.2485</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4</v>
+        <v>-1.8105</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2461</v>
+        <v>-0.4381</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7526</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6503</v>
+        <v>-0.3502</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0148</v>
+        <v>-0.1218</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3645</v>
+        <v>-0.2284</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5453</v>
+        <v>0.89</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.9863</v>
+        <v>0.89</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6444</v>
+        <v>-0.7508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4632</v>
+        <v>-0.7198</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1076</v>
+        <v>-0.031</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2545</v>
+        <v>0.2677</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5685</v>
+        <v>0.0216</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.686</v>
+        <v>0.2461</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.006</v>
+        <v>1.4215</v>
       </c>
       <c r="K6" t="n">
-        <v>1.242</v>
+        <v>1.4215</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.248</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2485</v>
+        <v>-1.1538</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8105</v>
+        <v>-1.4</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4381</v>
+        <v>0.2461</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5579</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8378</v>
+        <v>0.7478</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4208</v>
+        <v>0.8187</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.417</v>
+        <v>-0.0708</v>
       </c>
       <c r="V6" t="n">
-        <v>0.89</v>
+        <v>-2.5453</v>
       </c>
       <c r="W6" t="n">
-        <v>0.89</v>
+        <v>-1.9863</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3626</v>
+        <v>-0.9276</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9721</v>
+        <v>-0.3276</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3906</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6655</v>
+        <v>-2.3461</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3348</v>
+        <v>-1.1237</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6693</v>
+        <v>-1.2224</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2577</v>
+        <v>-0.6054</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9467</v>
+        <v>0.0591</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6889</v>
+        <v>-0.6645</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4078</v>
+        <v>-1.7407</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3881</v>
+        <v>-1.1829</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0197</v>
+        <v>-0.5578</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>1.1684</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3029</v>
+        <v>0.2501</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2594</v>
+        <v>0.2778</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0435</v>
+        <v>-0.0277</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7731</v>
+        <v>-1.0035</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9368</v>
+        <v>-1.5381</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1638</v>
+        <v>0.5347</v>
       </c>
       <c r="G8" t="n">
         <v>-0.829</v>
@@ -1078,13 +1078,13 @@
         <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2488</v>
+        <v>-0.4792</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0235</v>
+        <v>-0.6248</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2253</v>
+        <v>0.1456</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2795</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8147</v>
+        <v>-1.552</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-1.0717</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0884</v>
+        <v>-0.4803</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3461</v>
+        <v>-1.6655</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1237</v>
+        <v>-2.3348</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2224</v>
+        <v>0.6693</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6054</v>
+        <v>-0.2577</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0591</v>
+        <v>-0.9467</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6645</v>
+        <v>0.6889</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7407</v>
+        <v>-1.4078</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1829</v>
+        <v>-1.3881</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5578</v>
+        <v>-0.0197</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1684</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1684</v>
+        <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.637</v>
+        <v>0.1135</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1209</v>
+        <v>0.1597</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5161</v>
+        <v>-0.0462</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2755</v>
+        <v>-2.1976</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4857</v>
+        <v>-2.1039</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7898</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5503</v>
+        <v>-2.4927</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8011</v>
+        <v>-1.6887</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7492</v>
+        <v>-0.804</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.153</v>
+        <v>-1.8704</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.234</v>
+        <v>-1.2059</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.6645</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3973</v>
+        <v>-0.6224</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5671</v>
+        <v>-0.4829</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8302</v>
+        <v>-0.1395</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9117</v>
+        <v>-0.0944</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6673</v>
+        <v>-0.2335</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2444</v>
+        <v>0.1391</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4804</v>
+        <v>-2.7963</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3032</v>
+        <v>-1.0838</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1772</v>
+        <v>-1.7125</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4927</v>
+        <v>-2.5503</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6887</v>
+        <v>-1.8011</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.804</v>
+        <v>-0.7492</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8704</v>
+        <v>-1.153</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2059</v>
+        <v>-1.234</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6645</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6224</v>
+        <v>-1.3973</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4829</v>
+        <v>-0.5671</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1395</v>
+        <v>-0.8302</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3895</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3895</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3772</v>
+        <v>0.3909</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4328</v>
+        <v>0.0692</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0557</v>
+        <v>0.3216</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3309</v>
+        <v>-3.5807</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6095</v>
+        <v>-3.3137</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7214</v>
+        <v>-0.267</v>
       </c>
       <c r="G12" t="n">
         <v>-5.1835</v>
@@ -1390,13 +1390,13 @@
         <v>2.5316</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.901</v>
+        <v>-0.1509</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3327</v>
+        <v>-0.0369</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5684</v>
+        <v>-0.114</v>
       </c>
       <c r="V12" t="n">
         <v>1.1695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2388</v>
+        <v>-6.9149</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5447</v>
+        <v>-5.2425</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.694</v>
+        <v>-1.6724</v>
       </c>
       <c r="G13" t="n">
         <v>-6.9555</v>
@@ -1468,13 +1468,13 @@
         <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1325</v>
+        <v>1.4564</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8385</v>
+        <v>1.1408</v>
       </c>
       <c r="U13" t="n">
-        <v>0.294</v>
+        <v>0.3156</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2211</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.5001</v>
+        <v>-13.5066</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.206399999999999</v>
+        <v>-9.206499999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.293600000000001</v>
+        <v>-4.3002</v>
       </c>
       <c r="G14" t="n">
         <v>-21.04</v>
@@ -1546,19 +1546,19 @@
         <v>13.6315</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6522</v>
+        <v>3.6456</v>
       </c>
       <c r="T14" t="n">
         <v>2.8706</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2185</v>
+        <v>0.7751</v>
       </c>
       <c r="V14" t="n">
         <v>-2.928</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9117000000000003</v>
+        <v>0.9117000000000002</v>
       </c>
       <c r="X14" t="n">
         <v>-3.839700000000001</v>
